--- a/Assets/Scripts/Core/Parser/sfx.xlsx
+++ b/Assets/Scripts/Core/Parser/sfx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\OneDrive\바탕 화면\Dev\IdleGameProject\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Desktop\Dev\IdleRPG\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A0BA9E-FCF6-4A66-B010-17733DA4D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7C73C8-80BB-4947-99BA-1CBAA466030C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="1890" windowWidth="18210" windowHeight="12645" xr2:uid="{43B216CA-37FF-4019-9795-D941FD958536}"/>
+    <workbookView xWindow="29970" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{43B216CA-37FF-4019-9795-D941FD958536}"/>
   </bookViews>
   <sheets>
     <sheet name="SFX" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,6 +62,13 @@
   <si>
     <t>Dash</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OrcHit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exclusive</t>
   </si>
 </sst>
 </file>
@@ -480,7 +487,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -514,9 +521,18 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C3" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388610</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1111,7 +1127,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{6E4DC65B-0472-4E9D-8897-DFD0C108C240}">
-      <formula1>"bootstrap,title,main,dungeon"</formula1>
+      <formula1>"bootstrap,title,main,dungeon,exclusive"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Scripts/Core/Parser/sfx.xlsx
+++ b/Assets/Scripts/Core/Parser/sfx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Desktop\Dev\IdleRPG\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7C73C8-80BB-4947-99BA-1CBAA466030C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CA07C3-427A-40E8-919E-51564B22E318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29970" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{43B216CA-37FF-4019-9795-D941FD958536}"/>
+    <workbookView xWindow="30435" yWindow="2820" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{43B216CA-37FF-4019-9795-D941FD958536}"/>
   </bookViews>
   <sheets>
     <sheet name="SFX" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -69,6 +69,10 @@
   </si>
   <si>
     <t>exclusive</t>
+  </si>
+  <si>
+    <t>SkeletonHit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -536,9 +540,18 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C4" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388611</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">

--- a/Assets/Scripts/Core/Parser/sfx.xlsx
+++ b/Assets/Scripts/Core/Parser/sfx.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Desktop\Dev\IdleRPG\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\project-k\project-k\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02CA07C3-427A-40E8-919E-51564B22E318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19751AFE-5150-41A0-AC3E-A2A6C7C01998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30435" yWindow="2820" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{43B216CA-37FF-4019-9795-D941FD958536}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{43B216CA-37FF-4019-9795-D941FD958536}"/>
   </bookViews>
   <sheets>
     <sheet name="SFX" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -72,6 +72,30 @@
   </si>
   <si>
     <t>SkeletonHit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_Splash_SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parrying_SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slash_Attack_SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice_Block_SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Charge_Shot_SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tripple_Shot_SFX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -160,7 +184,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3814DACF-46B3-41F6-85BE-EE68AC2C339E}" name="표2" displayName="표2" ref="C1:C101" totalsRowShown="0">
   <autoFilter ref="C1:C101" xr:uid="{3814DACF-46B3-41F6-85BE-EE68AC2C339E}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{AF5BC49F-4C65-4A19-B79F-7CCDD9D64EE8}" name="MaskedId" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{AF5BC49F-4C65-4A19-B79F-7CCDD9D64EE8}" name="MaskedId" dataDxfId="0">
       <calculatedColumnFormula>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -182,7 +206,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{471E64AA-FBAF-4B32-9D38-BE1132AF7E17}" name="표4" displayName="표4" ref="C1:C101" totalsRowShown="0">
   <autoFilter ref="C1:C101" xr:uid="{471E64AA-FBAF-4B32-9D38-BE1132AF7E17}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{129F1963-EE71-4662-B246-36EF63A289E3}" name="MaskedId" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{129F1963-EE71-4662-B246-36EF63A289E3}" name="MaskedId" dataDxfId="1">
       <calculatedColumnFormula>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -191,9 +215,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -231,7 +255,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -337,7 +361,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -479,7 +503,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -488,14 +512,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A1AA8F-9B85-4EC0-87C4-5918A7534402}">
   <dimension ref="A1:D101"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="1" max="1" width="15.19921875" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -509,7 +533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -524,7 +548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -539,7 +563,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -554,583 +578,637 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C5" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C6" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C7" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C8" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C9" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C10" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388612</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388613</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388614</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388615</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388616</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388617</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C11" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C12" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C13" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C14" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C15" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C16" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C17" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C18" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C19" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C20" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C21" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C22" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C23" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C24" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C25" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C26" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C27" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C28" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C29" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C30" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C31" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C32" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C33" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C34" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C35" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C36" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C37" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C38" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C39" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C40" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C41" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C42" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C43" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C44" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C45" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C46" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C47" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C48" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C49" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C50" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C51" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C52" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C53" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C54" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C55" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C56" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C57" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C58" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C59" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C60" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C61" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C62" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C63" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C64" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C65" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C66" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C67" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C68" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C69" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C70" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C71" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C72" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C73" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C74" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C75" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C76" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C77" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C78" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C79" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C80" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C81" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C82" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C83" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C84" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C85" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C86" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C87" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C88" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C89" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C90" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C91" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C92" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C93" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C94" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C95" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C96" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C97" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C98" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C99" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C100" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C101" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
@@ -1154,12 +1232,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A3D028-3084-44DD-879B-5D1188588300}">
   <dimension ref="A1:D101"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1173,7 +1251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1188,595 +1266,595 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C3" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C4" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C5" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C6" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C7" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C8" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C9" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C10" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C11" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C12" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C13" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C14" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C15" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="C16" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C17" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C18" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C19" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C20" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C21" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C22" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C23" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C24" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C25" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C26" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C27" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C28" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C29" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C30" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C31" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C32" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C33" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C34" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C35" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C36" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C37" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C38" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C39" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C40" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C41" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C42" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C43" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C44" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C45" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C46" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C47" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C48" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C49" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C50" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C51" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C52" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C53" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C54" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C55" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C56" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C57" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C58" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C59" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C60" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C61" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C62" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C63" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C64" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C65" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C66" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C67" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C68" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C69" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C70" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C71" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C72" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C73" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C74" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C75" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C76" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C77" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C78" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C79" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C80" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C81" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C82" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C83" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C84" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C85" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C86" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C87" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C88" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C89" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C90" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C91" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C92" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C93" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C94" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C95" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C96" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C97" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C98" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C99" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C100" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C101" t="e">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v>#VALUE!</v>

--- a/Assets/Scripts/Core/Parser/sfx.xlsx
+++ b/Assets/Scripts/Core/Parser/sfx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\project-k\project-k\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19751AFE-5150-41A0-AC3E-A2A6C7C01998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70570717-A98F-4D3F-9332-F51E1CFF6337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{43B216CA-37FF-4019-9795-D941FD958536}"/>
+    <workbookView xWindow="-28320" yWindow="3945" windowWidth="17280" windowHeight="8880" xr2:uid="{43B216CA-37FF-4019-9795-D941FD958536}"/>
   </bookViews>
   <sheets>
     <sheet name="SFX" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -96,6 +96,22 @@
   </si>
   <si>
     <t>Tripple_Shot_SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire_Tornado_SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire_Tornado2_SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ice_Spike_SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lightning_SFX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -184,7 +200,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3814DACF-46B3-41F6-85BE-EE68AC2C339E}" name="표2" displayName="표2" ref="C1:C101" totalsRowShown="0">
   <autoFilter ref="C1:C101" xr:uid="{3814DACF-46B3-41F6-85BE-EE68AC2C339E}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{AF5BC49F-4C65-4A19-B79F-7CCDD9D64EE8}" name="MaskedId" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{AF5BC49F-4C65-4A19-B79F-7CCDD9D64EE8}" name="MaskedId" dataDxfId="1">
       <calculatedColumnFormula>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -206,7 +222,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{471E64AA-FBAF-4B32-9D38-BE1132AF7E17}" name="표4" displayName="표4" ref="C1:C101" totalsRowShown="0">
   <autoFilter ref="C1:C101" xr:uid="{471E64AA-FBAF-4B32-9D38-BE1132AF7E17}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{129F1963-EE71-4662-B246-36EF63A289E3}" name="MaskedId" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{129F1963-EE71-4662-B246-36EF63A289E3}" name="MaskedId" dataDxfId="0">
       <calculatedColumnFormula>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -514,7 +530,7 @@
   <dimension ref="A1:D101"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.19921875" customWidth="1"/>
+    <col min="1" max="1" width="17.8984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="10.5" customWidth="1"/>
   </cols>
@@ -669,27 +685,63 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C11" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388618</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C12" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388619</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C13" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388620</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C14" t="str">
-        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
-        <v/>
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
+        <v>8388621</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">

--- a/Assets/Scripts/Core/Parser/sfx.xlsx
+++ b/Assets/Scripts/Core/Parser/sfx.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\project-k\project-k\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\project-k\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70570717-A98F-4D3F-9332-F51E1CFF6337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62293FEF-6A28-4B1F-9C52-F8C85774ED32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28320" yWindow="3945" windowWidth="17280" windowHeight="8880" xr2:uid="{43B216CA-37FF-4019-9795-D941FD958536}"/>
+    <workbookView xWindow="765" yWindow="2580" windowWidth="25815" windowHeight="11295" xr2:uid="{43B216CA-37FF-4019-9795-D941FD958536}"/>
   </bookViews>
   <sheets>
     <sheet name="SFX" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>fileName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -112,6 +112,22 @@
   </si>
   <si>
     <t>Lightning_SFX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>main</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TITLE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -231,9 +247,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -271,7 +287,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -377,7 +393,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -519,7 +535,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -528,14 +544,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A1AA8F-9B85-4EC0-87C4-5918A7534402}">
   <dimension ref="A1:D101"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -549,7 +565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -564,7 +580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -579,7 +595,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -594,7 +610,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -609,7 +625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -624,7 +640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -639,7 +655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -654,7 +670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -669,7 +685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -684,7 +700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -699,7 +715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -714,7 +730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -729,7 +745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -744,523 +760,523 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C15" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C16" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C18" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C19" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C20" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C21" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C22" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C23" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C24" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C25" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C26" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C27" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C28" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C29" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C30" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C31" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C32" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C34" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C35" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C36" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C37" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C38" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C39" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C40" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C41" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C42" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C43" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C44" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C45" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C46" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C47" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C48" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C49" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C50" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C51" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C52" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C53" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C54" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C55" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C56" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C57" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C58" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C59" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C60" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C61" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C62" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C63" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C64" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C65" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C66" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C67" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C68" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C69" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C70" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C71" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C72" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C73" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C74" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C75" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C76" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C77" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C78" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C79" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C80" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C81" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C82" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C83" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C84" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C85" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C86" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C87" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C88" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C89" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C90" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C91" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C92" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C93" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C94" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C95" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C96" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C97" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C98" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C99" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C100" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C101" t="str">
         <f>IF(표1[[#This Row],[Id]]="","",_xlfn.BITOR(표1[[#This Row],[Id]],8388608))</f>
         <v/>
@@ -1284,12 +1300,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A3D028-3084-44DD-879B-5D1188588300}">
   <dimension ref="A1:D101"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1303,7 +1319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1318,595 +1334,613 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C3" t="str">
-        <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="C4" t="str">
-        <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
+        <v>12582914</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
+        <v>12582915</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C5" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C6" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C7" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C8" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C9" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C10" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C11" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C12" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C13" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C14" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C15" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C16" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C18" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C19" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C20" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C21" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C22" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C23" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C24" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C25" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C26" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C27" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C28" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C29" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C30" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C31" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C32" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C34" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C35" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C36" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C37" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C38" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C39" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C40" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C41" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C42" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C43" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C44" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C45" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C46" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C47" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C48" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C49" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C50" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C51" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C52" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C53" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C54" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C55" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C56" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C57" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C58" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C59" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C60" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C61" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C62" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C63" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C64" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C65" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C66" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C67" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C68" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C69" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C70" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C71" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C72" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C73" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C74" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C75" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C76" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C77" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C78" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C79" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C80" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C81" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C82" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C83" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C84" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C85" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C86" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C87" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C88" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C89" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C90" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C91" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C92" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C93" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C94" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C95" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C96" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C97" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C98" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C99" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C100" t="str">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.4">
+    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C101" t="e">
         <f>IF(표3[[#This Row],[Id]] = "","",_xlfn.BITOR(표3[[#This Row],[Id]],12582912))</f>
         <v>#VALUE!</v>
